--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:23:16+00:00</t>
+    <t>2026-08-10T12:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理WSIのDICOM画像に関する情報を扱うためのプロファイル</t>
+    <t>病理WSIのDICOM画像に関する情報を記録するためのプロファイル</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -511,7 +511,8 @@
     <t>DICOM画像のステータス</t>
   </si>
   <si>
-    <t>登録済み | 利用可能 | 取消済み | エラーで入力 | 不明 http://hl7.org/fhir/ValueSet/imagingstudy-status|4.0.1</t>
+    <t>登録済み | 利用可能 | 取消済み | エラーで入力 | 不明
+http://hl7.org/fhir/ValueSet/imagingstudy-status</t>
   </si>
   <si>
     <t>required</t>
@@ -674,7 +675,8 @@
     <t>他のシステムから依頼されたオーダ情報。</t>
   </si>
   <si>
-    <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
+    <t>通常、依頼元となるServiceRequestリソースを参照する。
+他のシステムと連携していない場合は参照不要。</t>
   </si>
   <si>
     <t>To support grouped procedures (one imaging study supporting multiple ordered procedures, e.g. chest/abdomen/pelvis CT).</t>
@@ -699,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -750,7 +752,8 @@
     <t>画像を診断した医師。</t>
   </si>
   <si>
-    <t>通常、病理医。病理では原則使用しない。</t>
+    <t>通常、病理医。
+病理では原則使用しない。</t>
   </si>
   <si>
     <t>Access methods for viewing (e.g., IHE’s IID profile) or retrieving (e.g., DICOM’s WADO-URI and WADO-RS) the study or the study’s series or instances. The study-level baseLocation applies to each series in the study, unless overridden in series by a series-level baseLocation of the same type.</t>
@@ -837,7 +840,8 @@
     <t>実施された処置に関する情報。</t>
   </si>
   <si>
-    <t>病理では省略してよい。使用する場合には、JP Core Procedureを参照する。</t>
+    <t>病理では省略してよい。
+使用する場合には、JP Core Procedureを参照する。</t>
   </si>
   <si>
     <t>実行されたプロシジャー（処置等）のタイプ。</t>
@@ -852,7 +856,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -916,7 +920,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|Media|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference|Media)
 </t>
   </si>
   <si>
@@ -1091,7 +1095,8 @@
     <t>このシリーズが取得された撮影装置（モダリティ）。</t>
   </si>
   <si>
-    <t>病理（WSI）を表すモダリティコード"SM"を指定する。1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
+    <t>病理（WSI）を表すモダリティコード"SM"を指定する。
+1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
   </si>
   <si>
     <t>(0008,0060)</t>
@@ -1270,7 +1275,7 @@
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1345,7 +1350,8 @@
     <t>SOPクラスUID。</t>
   </si>
   <si>
-    <t>病理では、主に以下の値が指定される。VL Whole Slide Microscopy Image Storage (VL全スライド顕微鏡画像保存): 1.2.840.10008.5.1.4.1.1.77.1.6</t>
+    <t>病理では、主に以下の値が指定される。
+VL Whole Slide Microscopy Image Storage (VL全スライド顕微鏡画像保存): 1.2.840.10008.5.1.4.1.1.77.1.6</t>
   </si>
   <si>
     <t>インスタンスのSOPクラス。</t>
@@ -1714,7 +1720,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="220.078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:51:50+00:00</t>
+    <t>2026-08-12T07:04:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理WSIのDICOM画像に関する情報を記録するためのプロファイル</t>
+    <t>このプロファイルはImagingStudyリソースに対して、病理WSIのDICOM画像に関するデータを送受信するための制約と拡張を定めたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -478,7 +478,7 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像全体を一意に識別するためのID。【詳細参照】</t>
+    <t>DICOM画像全体を一意に識別するためのID【詳細参照】</t>
   </si>
   <si>
     <t>DICOM画像全体を一意に識別するためのID。</t>
@@ -511,8 +511,7 @@
     <t>DICOM画像のステータス</t>
   </si>
   <si>
-    <t>登録済み | 利用可能 | 取消済み | エラーで入力 | 不明
-http://hl7.org/fhir/ValueSet/imagingstudy-status</t>
+    <t>登録済み | 利用可能 | 取消済み | エラーで入力 | 不明 http://hl7.org/fhir/ValueSet/imagingstudy-status|4.0.1</t>
   </si>
   <si>
     <t>required</t>
@@ -581,7 +580,7 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像の対象患者に関する情報。【詳細参照】</t>
+    <t>DICOM画像の対象患者に関する情報【詳細参照】</t>
   </si>
   <si>
     <t>DICOM画像の対象患者に関する情報。</t>
@@ -609,7 +608,7 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像を取得するきっかけとなった情報。【詳細参照】</t>
+    <t>このDICOM画像を取得するきっかけとなった情報【詳細参照】</t>
   </si>
   <si>
     <t>このDICOM画像を取得するきっかけとなった情報。</t>
@@ -638,7 +637,7 @@
 </t>
   </si>
   <si>
-    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時。【詳細参照】</t>
+    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時【詳細参照】</t>
   </si>
   <si>
     <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時。</t>
@@ -669,14 +668,13 @@
 </t>
   </si>
   <si>
-    <t>他のシステムから依頼されたオーダ情報。【詳細参照】</t>
+    <t>他のシステムから依頼されたオーダ情報【詳細参照】</t>
   </si>
   <si>
     <t>他のシステムから依頼されたオーダ情報。</t>
   </si>
   <si>
-    <t>通常、依頼元となるServiceRequestリソースを参照する。
-他のシステムと連携していない場合は参照不要。</t>
+    <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
   </si>
   <si>
     <t>To support grouped procedures (one imaging study supporting multiple ordered procedures, e.g. chest/abdomen/pelvis CT).</t>
@@ -705,7 +703,13 @@
 </t>
   </si>
   <si>
-    <t>依頼医師。必須ではない（ServiceRequestから参照できるため）。</t>
+    <t>依頼医師【詳細参照】</t>
+  </si>
+  <si>
+    <t>依頼医師。</t>
+  </si>
+  <si>
+    <t>病理では、原則使用しない。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target[classCode=DGIMG, moodCode=RQO].participation[typeCode=AUT].role</t>
@@ -721,13 +725,13 @@
 </t>
   </si>
   <si>
-    <t>依頼医師。【詳細参照】</t>
-  </si>
-  <si>
-    <t>依頼医師。</t>
-  </si>
-  <si>
-    <t>病理では、原則使用しない。</t>
+    <t>画像を診断した医師【詳細参照】</t>
+  </si>
+  <si>
+    <t>画像を診断した医師。</t>
+  </si>
+  <si>
+    <t>通常、病理医。病理では原則使用しない。</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF].role</t>
@@ -746,14 +750,13 @@
 </t>
   </si>
   <si>
-    <t>画像を診断した医師。【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像を診断した医師。</t>
-  </si>
-  <si>
-    <t>通常、病理医。
-病理では原則使用しない。</t>
+    <t>DICOMのリソースが存在する位置【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOMのリソースが存在する位置。</t>
+  </si>
+  <si>
+    <t>DICOM WADO-RS、DICOM WADO-URI、DICOM QIDO-RSなどを指定する。</t>
   </si>
   <si>
     <t>Access methods for viewing (e.g., IHE’s IID profile) or retrieving (e.g., DICOM’s WADO-URI and WADO-RS) the study or the study’s series or instances. The study-level baseLocation applies to each series in the study, unless overridden in series by a series-level baseLocation of the same type.</t>
@@ -773,13 +776,7 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像リソースが存在する位置。【詳細参照】</t>
-  </si>
-  <si>
-    <t>このDICOM画像リソースが存在する位置。</t>
-  </si>
-  <si>
-    <t>基本的には1つ指定する。</t>
+    <t>このDICOM画像検査に含まれるシリーズ数。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=OBSSER, moodCode=EVN].repeatNumber</t>
@@ -795,7 +792,7 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像検査に含まれるシリーズ数。</t>
+    <t>このDICOM画像に含まれるイメージ（インスタンス）の数。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=DGIMG, moodCode=EVN].repeatNumber</t>
@@ -811,7 +808,13 @@
 </t>
   </si>
   <si>
-    <t>このDICOM画像に含まれるイメージ（インスタンス）の数。</t>
+    <t>実施された処置に関する情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>実施された処置に関する情報。</t>
+  </si>
+  <si>
+    <t>病理では省略してよい。使用する場合には、JP Core Procedureを参照する。</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -834,14 +837,13 @@
 </t>
   </si>
   <si>
-    <t>実施された処置に関する情報。【詳細参照】</t>
-  </si>
-  <si>
-    <t>実施された処置に関する情報。</t>
-  </si>
-  <si>
-    <t>病理では省略してよい。
-使用する場合には、JP Core Procedureを参照する。</t>
+    <t>実施された処置を表すコード【詳細参照】</t>
+  </si>
+  <si>
+    <t>実施された処置を表すコード。</t>
+  </si>
+  <si>
+    <t>病理では原則使用しない。</t>
   </si>
   <si>
     <t>実行されたプロシジャー（処置等）のタイプ。</t>
@@ -860,13 +862,7 @@
 </t>
   </si>
   <si>
-    <t>実施された処置を表すコード。【詳細参照】</t>
-  </si>
-  <si>
-    <t>実施された処置を表すコード。</t>
-  </si>
-  <si>
-    <t>病理では原則使用しない。</t>
+    <t>ImagingStudyが実行された場所（画像がスキャンされた場所）を示すLocationリソースがある場合には、これを参照。</t>
   </si>
   <si>
     <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
@@ -890,10 +886,10 @@
     <t>ImagingStudy.reasonCode</t>
   </si>
   <si>
-    <t>検査目的【詳細参照】</t>
-  </si>
-  <si>
-    <t>検査目的</t>
+    <t>DICOM画像が依頼された理由を表す1つ以上のコード【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOM画像が依頼された理由を表す1つ以上のコード。</t>
   </si>
   <si>
     <t>example</t>
@@ -920,14 +916,17 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference|Media)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Pathology)
 </t>
   </si>
   <si>
-    <t>DICOM画像が依頼された理由を表す1つ以上のコード。【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像が依頼された理由を表す1つ以上のコード。</t>
+    <t>DICOM画像の実施理由に関する情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOM画像の実施理由に関する情報。</t>
+  </si>
+  <si>
+    <t>JP Core DiagnosticReportリソースを参照する。</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -946,13 +945,7 @@
 </t>
   </si>
   <si>
-    <t>DICOM画像の実施理由に関する情報。【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像の実施理由に関する情報。</t>
-  </si>
-  <si>
-    <t>JP Core DiagnosticReportリソースを参照する。</t>
+    <t>原則、未使用</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1042,7 +1035,7 @@
 </t>
   </si>
   <si>
-    <t>シリーズを識別する一意に識別するためのUID。【詳細参照】</t>
+    <t>シリーズを識別する一意に識別するためのUID【詳細参照】</t>
   </si>
   <si>
     <t>シリーズを識別する一意に識別するためのUID。</t>
@@ -1089,14 +1082,13 @@
 </t>
   </si>
   <si>
-    <t>このシリーズが取得された撮影装置（モダリティ）。【詳細参照】</t>
+    <t>このシリーズが取得された撮影装置（モダリティ）【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズが取得された撮影装置（モダリティ）。</t>
   </si>
   <si>
-    <t>病理（WSI）を表すモダリティコード"SM"を指定する。
-1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
+    <t>病理（WSI）を表すモダリティコード"SM"を指定する。1シリーズ1モダリティで、1つのシリーズの中に複数のモダリティが混在することはない。</t>
   </si>
   <si>
     <t>(0008,0060)</t>
@@ -1150,7 +1142,7 @@
 </t>
   </si>
   <si>
-    <t>このシリーズの対象となる解剖学的部位。【詳細参照】</t>
+    <t>このシリーズの対象となる解剖学的部位【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズの対象となる解剖学的部位。</t>
@@ -1171,7 +1163,7 @@
     <t>ImagingStudy.series.laterality</t>
   </si>
   <si>
-    <t>解剖学的部位の左右。【詳細参照】</t>
+    <t>解剖学的部位の左右【詳細参照】</t>
   </si>
   <si>
     <t>解剖学的部位の左右。</t>
@@ -1189,11 +1181,11 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Pathology)
 </t>
   </si>
   <si>
-    <t>このシリーズの検体に関する情報。【詳細参照】</t>
+    <t>このシリーズの検体に関する情報【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズの検体に関する情報。</t>
@@ -1211,7 +1203,7 @@
     <t>ImagingStudy.series.started</t>
   </si>
   <si>
-    <t>このシリーズの開始日時。【詳細参照】</t>
+    <t>このシリーズの開始日時【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズの開始日時。</t>
@@ -1230,7 +1222,7 @@
 OperatorName</t>
   </si>
   <si>
-    <t>このシリーズの実施医。【詳細参照】</t>
+    <t>このシリーズの実施医【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズの実施医。</t>
@@ -1257,7 +1249,7 @@
     <t>ImagingStudy.series.performer.function</t>
   </si>
   <si>
-    <t>このシリーズの実施医の役割。【詳細参照】</t>
+    <t>このシリーズの実施医の役割【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズの実施医の役割。</t>
@@ -1279,7 +1271,7 @@
 </t>
   </si>
   <si>
-    <t>このシリーズの撮影者、もしくは組織。【詳細参照】</t>
+    <t>このシリーズの撮影者、もしくは組織【詳細参照】</t>
   </si>
   <si>
     <t>このシリーズの撮影者、もしくは組織。</t>
@@ -1319,13 +1311,13 @@
 </t>
   </si>
   <si>
-    <t>インスタンス（画像）のユニークID。【詳細参照】</t>
+    <t>インスタンス（画像）のユニークID【詳細参照】</t>
   </si>
   <si>
     <t>インスタンス（画像）のユニークID。</t>
   </si>
   <si>
-    <t>SOP Instance UID (0008,0018) に入力されている値を指定する。</t>
+    <t>SOP Instance UID (0008,0018) に値が入っていれば、その値を指定する。</t>
   </si>
   <si>
     <t>DICOM SOP Instance UID.</t>
@@ -1344,14 +1336,13 @@
 </t>
   </si>
   <si>
-    <t>SOPクラスUID。【詳細参照】</t>
+    <t>SOPクラスUID【詳細参照】</t>
   </si>
   <si>
     <t>SOPクラスUID。</t>
   </si>
   <si>
-    <t>病理では、主に以下の値が指定される。
-VL Whole Slide Microscopy Image Storage (VL全スライド顕微鏡画像保存): 1.2.840.10008.5.1.4.1.1.77.1.6</t>
+    <t>病理では、主に以下の値が指定される。VL Whole Slide Microscopy Image Storage (VL全スライド顕微鏡画像保存): 1.2.840.10008.5.1.4.1.1.77.1.6</t>
   </si>
   <si>
     <t>インスタンスのSOPクラス。</t>
@@ -1373,7 +1364,7 @@
 </t>
   </si>
   <si>
-    <t>SOP Instance UIDとは別に、ユーザー（または装置）が自由に決められるインスタンス（画像）ごとの番号。【詳細参照】</t>
+    <t>SOP Instance UIDとは別に、ユーザー（または装置）が自由に決められるインスタンス（画像）ごとの番号【詳細参照】</t>
   </si>
   <si>
     <t>SOP Instance UIDとは別に、ユーザー（または装置）が自由に決められるインスタンス（画像）ごとの番号。</t>
@@ -1391,7 +1382,7 @@
     <t>ImagingStudy.series.instance.title</t>
   </si>
   <si>
-    <t>画像に関する説明。【詳細参照】</t>
+    <t>画像に関する説明【詳細参照】</t>
   </si>
   <si>
     <t>画像に関する説明。</t>
@@ -3785,9 +3776,11 @@
         <v>221</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3854,10 +3847,10 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>217</v>
@@ -3868,14 +3861,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3897,13 +3890,13 @@
         <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3953,7 +3946,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3971,13 +3964,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -3985,10 +3978,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4011,19 +4004,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4072,7 +4065,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4090,7 +4083,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4104,14 +4097,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4130,17 +4123,15 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N21" t="s" s="2">
         <v>244</v>
       </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4189,7 +4180,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4247,7 +4238,7 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>249</v>
@@ -4368,9 +4359,11 @@
         <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4434,13 +4427,13 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4451,14 +4444,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4477,16 +4470,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4515,10 +4508,10 @@
         <v>174</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4536,7 +4529,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4551,13 +4544,13 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4568,10 +4561,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4594,17 +4587,15 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>271</v>
       </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>272</v>
       </c>
@@ -4655,7 +4646,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4713,7 +4704,7 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>279</v>
@@ -4722,7 +4713,7 @@
         <v>280</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4839,7 +4830,7 @@
         <v>291</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4904,10 +4895,10 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -4916,15 +4907,15 @@
         <v>287</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4947,17 +4938,15 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>299</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5006,7 +4995,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5021,10 +5010,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5038,14 +5027,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5064,13 +5053,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5121,7 +5110,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5139,10 +5128,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5153,10 +5142,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5179,13 +5168,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5236,7 +5225,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5254,7 +5243,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5268,10 +5257,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5294,13 +5283,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5351,7 +5340,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5369,7 +5358,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5383,10 +5372,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5415,7 +5404,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5468,7 +5457,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5486,7 +5475,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5500,14 +5489,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5529,10 +5518,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>138</v>
@@ -5587,7 +5576,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5619,14 +5608,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5648,16 +5637,16 @@
         <v>91</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5670,7 +5659,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5706,7 +5695,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>89</v>
@@ -5724,10 +5713,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5738,14 +5727,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5764,13 +5753,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5785,7 +5774,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5821,7 +5810,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5839,10 +5828,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5853,14 +5842,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5882,13 +5871,13 @@
         <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5938,7 +5927,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -5959,7 +5948,7 @@
         <v>177</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -5970,14 +5959,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5996,13 +5985,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6017,7 +6006,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6053,7 +6042,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6071,10 +6060,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6085,14 +6074,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6111,13 +6100,13 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6168,7 +6157,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6189,7 +6178,7 @@
         <v>250</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6200,10 +6189,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6226,19 +6215,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6287,7 +6276,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6305,7 +6294,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6319,14 +6308,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6348,13 +6337,13 @@
         <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="N40" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6383,11 +6372,11 @@
         <v>281</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6404,7 +6393,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6422,10 +6411,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6436,10 +6425,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6465,13 +6454,13 @@
         <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="N41" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6500,11 +6489,11 @@
         <v>281</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6521,7 +6510,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6539,10 +6528,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6553,10 +6542,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6579,16 +6568,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6638,7 +6627,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6656,10 +6645,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6670,10 +6659,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6699,13 +6688,13 @@
         <v>199</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6755,7 +6744,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6776,7 +6765,7 @@
         <v>205</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6787,14 +6776,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6813,19 +6802,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6874,7 +6863,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6889,13 +6878,13 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6906,10 +6895,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6932,13 +6921,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6989,7 +6978,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7007,7 +6996,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7021,10 +7010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7053,7 +7042,7 @@
         <v>136</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>138</v>
@@ -7106,7 +7095,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7124,7 +7113,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7138,14 +7127,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7167,10 +7156,10 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>138</v>
@@ -7225,7 +7214,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7257,10 +7246,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7283,19 +7272,19 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7323,11 +7312,11 @@
         <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7344,7 +7333,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7362,7 +7351,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7376,10 +7365,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7402,16 +7391,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7461,7 +7450,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7479,24 +7468,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7519,13 +7508,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7576,7 +7565,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7594,7 +7583,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7608,10 +7597,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7634,13 +7623,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7691,7 +7680,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7709,7 +7698,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7723,10 +7712,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7755,7 +7744,7 @@
         <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>138</v>
@@ -7808,7 +7797,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7826,7 +7815,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7840,14 +7829,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7869,10 +7858,10 @@
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>138</v>
@@ -7927,7 +7916,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7959,14 +7948,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7988,16 +7977,16 @@
         <v>91</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8010,7 +7999,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8046,7 +8035,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>89</v>
@@ -8064,10 +8053,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8078,14 +8067,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8107,13 +8096,13 @@
         <v>170</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8142,11 +8131,11 @@
         <v>174</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8163,7 +8152,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>89</v>
@@ -8181,10 +8170,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8195,14 +8184,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8221,16 +8210,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8280,7 +8269,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8298,10 +8287,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8312,10 +8301,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8338,16 +8327,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8397,7 +8386,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8415,10 +8404,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:04:31+00:00</t>
+    <t>2026-08-12T07:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:45:23+00:00</t>
+    <t>2026-08-12T12:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -573,6 +573,176 @@
     <t>FiveWs.class</t>
   </si>
   <si>
+    <t>ImagingStudy.modality.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
     <t>ImagingStudy.subject</t>
   </si>
   <si>
@@ -961,10 +1131,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>DICOM画像に関する記述。</t>
   </si>
   <si>
@@ -996,19 +1162,10 @@
     <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。</t>
   </si>
   <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>ImagingStudy.series.extension</t>
   </si>
   <si>
     <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>ImagingStudy.series.modifierExtension</t>
@@ -1092,6 +1249,27 @@
   </si>
   <si>
     <t>(0008,0060)</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.id</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.extension</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.system</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.version</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.code</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.display</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.modality.userSelected</t>
   </si>
   <si>
     <t>ImagingStudy.series.description</t>
@@ -1698,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.13671875" customWidth="true" bestFit="true"/>
@@ -1729,7 +1907,7 @@
     <col min="26" max="26" width="74.78125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="32.90234375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1740,7 +1918,7 @@
     <col min="38" max="38" width="97.94921875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="89.92578125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="32.41015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3285,7 +3463,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -3297,7 +3475,7 @@
         <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>181</v>
@@ -3308,9 +3486,7 @@
       <c r="M14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>184</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3359,10 +3535,10 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>89</v>
@@ -3371,19 +3547,19 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3391,21 +3567,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3414,19 +3590,19 @@
         <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3464,43 +3640,43 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3508,14 +3684,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3534,18 +3710,20 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3557,7 +3735,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3593,7 +3771,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3605,30 +3783,30 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3639,7 +3817,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -3651,20 +3829,18 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3718,40 +3894,40 @@
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3770,24 +3946,24 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3829,7 +4005,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3841,41 +4017,41 @@
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -3887,18 +4063,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -3946,42 +4122,42 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3992,7 +4168,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -4004,19 +4180,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4065,50 +4241,50 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4123,15 +4299,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4180,10 +4358,10 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>89</v>
@@ -4195,16 +4373,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4212,14 +4390,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4238,15 +4416,17 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4295,7 +4475,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4310,16 +4490,16 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>250</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4334,7 +4514,7 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4353,16 +4533,16 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4376,7 +4556,7 @@
         <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>79</v>
@@ -4427,16 +4607,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4444,14 +4624,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4470,18 +4650,20 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4505,13 +4687,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4529,7 +4711,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4544,16 +4726,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4561,14 +4743,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4587,18 +4769,18 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4646,7 +4828,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4661,31 +4843,31 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4704,16 +4886,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4739,31 +4921,31 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4778,16 +4960,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4795,10 +4977,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4821,18 +5003,20 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4880,7 +5064,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4895,19 +5079,19 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -4919,14 +5103,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -4938,13 +5122,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5001,7 +5185,7 @@
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
@@ -5010,13 +5194,13 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>300</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
@@ -5027,14 +5211,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5053,7 +5237,7 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>304</v>
@@ -5110,7 +5294,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5156,7 +5340,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5174,9 +5358,11 @@
         <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5231,7 +5417,7 @@
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5240,13 +5426,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
@@ -5257,21 +5443,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5280,18 +5466,20 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5316,13 +5504,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5340,28 +5528,28 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
@@ -5372,21 +5560,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5395,21 +5583,21 @@
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>325</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5457,46 +5645,46 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5509,26 +5697,24 @@
         <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5552,13 +5738,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5576,7 +5762,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5588,19 +5774,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>132</v>
+        <v>340</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5608,21 +5794,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5634,20 +5820,18 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>91</v>
+        <v>344</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5659,7 +5843,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5695,13 +5879,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -5710,38 +5894,38 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -5753,13 +5937,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>352</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5774,7 +5958,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5810,13 +5994,13 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
@@ -5825,13 +6009,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5842,18 +6026,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -5868,17 +6052,15 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5903,13 +6085,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -5927,10 +6109,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -5945,10 +6127,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>177</v>
+        <v>359</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -5959,21 +6141,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -5985,13 +6167,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6006,7 +6188,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6042,13 +6224,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -6060,10 +6242,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6074,14 +6256,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6097,16 +6279,16 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>243</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6157,7 +6339,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>184</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6169,16 +6351,16 @@
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6189,14 +6371,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6212,23 +6394,21 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6276,7 +6456,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>193</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6288,13 +6468,13 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6308,44 +6488,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6369,13 +6551,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6393,28 +6575,28 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>132</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6425,18 +6607,18 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -6451,18 +6633,20 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6474,7 +6658,7 @@
         <v>79</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>79</v>
@@ -6486,13 +6670,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6510,10 +6694,10 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -6528,10 +6712,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6542,21 +6726,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6568,17 +6752,15 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>298</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6591,7 +6773,7 @@
         <v>79</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>79</v>
@@ -6627,13 +6809,13 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
@@ -6645,10 +6827,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6659,18 +6841,18 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6685,16 +6867,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6720,13 +6902,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6744,10 +6926,10 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -6762,10 +6944,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6776,21 +6958,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6799,23 +6981,19 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>308</v>
+        <v>181</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>182</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -6863,28 +7041,28 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6895,21 +7073,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -6921,15 +7099,17 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>303</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>312</v>
+        <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -6966,37 +7146,37 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>193</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7010,21 +7190,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7033,21 +7213,23 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7095,25 +7277,25 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>318</v>
+        <v>200</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>315</v>
+        <v>202</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7122,51 +7304,49 @@
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>321</v>
+        <v>205</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>322</v>
+        <v>206</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7214,25 +7394,25 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>323</v>
+        <v>208</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7241,15 +7421,15 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7272,26 +7452,24 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>395</v>
+        <v>212</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>397</v>
+        <v>214</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>79</v>
@@ -7309,13 +7487,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7333,7 +7511,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>394</v>
+        <v>216</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7345,13 +7523,13 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7360,15 +7538,15 @@
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7376,7 +7554,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7391,18 +7569,18 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>401</v>
+        <v>181</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>402</v>
+        <v>220</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7450,10 +7628,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>400</v>
+        <v>223</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
@@ -7462,30 +7640,30 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>404</v>
+        <v>224</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>405</v>
+        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>406</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7496,7 +7674,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7505,19 +7683,23 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>408</v>
+        <v>228</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7565,25 +7747,25 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>232</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>409</v>
+        <v>233</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7592,19 +7774,19 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7620,16 +7802,16 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>312</v>
+        <v>405</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>313</v>
+        <v>405</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7644,7 +7826,7 @@
         <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>79</v>
@@ -7680,7 +7862,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7692,16 +7874,16 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -7712,21 +7894,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>134</v>
+        <v>409</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7735,20 +7917,18 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>298</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>136</v>
+        <v>410</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7797,28 +7977,28 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>408</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -7836,7 +8016,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7849,25 +8029,25 @@
         <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>290</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>321</v>
+        <v>413</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>138</v>
+        <v>414</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>144</v>
+        <v>415</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -7916,7 +8096,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7928,13 +8108,13 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>132</v>
+        <v>295</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7948,18 +8128,18 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -7971,23 +8151,21 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -7999,7 +8177,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>419</v>
+        <v>79</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8011,13 +8189,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8035,10 +8213,10 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>89</v>
@@ -8053,10 +8231,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8067,18 +8245,18 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8090,19 +8268,19 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>170</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>425</v>
+        <v>320</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8128,13 +8306,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8152,10 +8330,10 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>89</v>
@@ -8170,7 +8348,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>429</v>
@@ -8191,14 +8369,14 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>431</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8207,10 +8385,10 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>243</v>
+        <v>431</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>432</v>
@@ -8233,7 +8411,7 @@
         <v>79</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>79</v>
@@ -8275,7 +8453,7 @@
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8324,10 +8502,10 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>438</v>
@@ -8404,15 +8582,1657 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="B58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:14:47+00:00</t>
+    <t>2026-08-12T12:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:53:42+00:00</t>
+    <t>2026-08-12T13:21:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:21:20+00:00</t>
+    <t>2026-08-13T00:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:17:30+00:00</t>
+    <t>2026-08-13T00:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:49:15+00:00</t>
+    <t>2026-08-13T01:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:04:13+00:00</t>
+    <t>2026-08-13T01:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:37:50+00:00</t>
+    <t>2026-08-13T08:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -555,582 +555,420 @@
     <t>病理（WSI）を表すモダリティコード"SM"を指定する。</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://dicom.nema.org/resources/ontology/DCM"/&gt;
+  &lt;code value="SM"/&gt;
+  &lt;display value="Slide Microscopy"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>(0008,0061)</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>ImagingStudy.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+</t>
+  </si>
+  <si>
+    <t>DICOM画像の対象患者に関する情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOM画像の対象患者に関する情報。</t>
+  </si>
+  <si>
+    <t>JP Core Patientリソースを参照する。</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role</t>
+  </si>
+  <si>
+    <t>(0010/*)</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>ImagingStudy.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+</t>
+  </si>
+  <si>
+    <t>このDICOM画像を取得するきっかけとなった情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>このDICOM画像を取得するきっかけとなった情報。</t>
+  </si>
+  <si>
+    <t>JP Core Encounterリソースを参照する。</t>
+  </si>
+  <si>
+    <t>Event.encounter</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>ImagingStudy.started</t>
+  </si>
+  <si>
+    <t>StudyDate
+StudyTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時【詳細参照】</t>
+  </si>
+  <si>
+    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時。</t>
+  </si>
+  <si>
+    <t>病理では、検体採取日時。</t>
+  </si>
+  <si>
+    <t>2011-01-01T11:01:20+03:00</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>(0008,0020)+(0008,0030)</t>
+  </si>
+  <si>
+    <t>FiveWs.init</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>他のシステムから依頼されたオーダ情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>他のシステムから依頼されたオーダ情報。</t>
+  </si>
+  <si>
+    <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
+  </si>
+  <si>
+    <t>To support grouped procedures (one imaging study supporting multiple ordered procedures, e.g. chest/abdomen/pelvis CT).</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target[classCode=DGIMG, moodCode=RQO]</t>
+  </si>
+  <si>
+    <t>(0032,1064)</t>
+  </si>
+  <si>
+    <t>FiveWs.cause</t>
+  </si>
+  <si>
+    <t>ImagingStudy.referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ReferringPhysiciansName
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>依頼医師【詳細参照】</t>
+  </si>
+  <si>
+    <t>依頼医師。</t>
+  </si>
+  <si>
+    <t>病理では、原則使用しない。</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target[classCode=DGIMG, moodCode=RQO].participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>(0008,0090)+(0008,0096)</t>
+  </si>
+  <si>
+    <t>ImagingStudy.interpreter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of Physician(s) Reading Study
+</t>
+  </si>
+  <si>
+    <t>画像を診断した医師【詳細参照】</t>
+  </si>
+  <si>
+    <t>画像を診断した医師。</t>
+  </si>
+  <si>
+    <t>通常、病理医。病理では原則使用しない。</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role</t>
+  </si>
+  <si>
+    <t>(0008,1060)</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>ImagingStudy.endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>DICOMのリソースが存在する位置【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOMのリソースが存在する位置。</t>
+  </si>
+  <si>
+    <t>DICOM WADO-RS、DICOM WADO-URI、DICOM QIDO-RSなどを指定する。</t>
+  </si>
+  <si>
+    <t>Access methods for viewing (e.g., IHE’s IID profile) or retrieving (e.g., DICOM’s WADO-URI and WADO-RS) the study or the study’s series or instances. The study-level baseLocation applies to each series in the study, unless overridden in series by a series-level baseLocation of the same type.</t>
+  </si>
+  <si>
+    <t>Not supported</t>
+  </si>
+  <si>
+    <t>ImagingStudy.numberOfSeries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NumberOfStudyRelatedSeries
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>このDICOM画像検査に含まれるシリーズ数。</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=OBSSER, moodCode=EVN].repeatNumber</t>
+  </si>
+  <si>
+    <t>(0020,1206)</t>
+  </si>
+  <si>
+    <t>ImagingStudy.numberOfInstances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NumberOfStudyRelatedInstances
+</t>
+  </si>
+  <si>
+    <t>このDICOM画像に含まれるイメージ（インスタンス）の数。</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=DGIMG, moodCode=EVN].repeatNumber</t>
+  </si>
+  <si>
+    <t>(0020,1208)</t>
+  </si>
+  <si>
+    <t>ImagingStudy.procedureReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+</t>
+  </si>
+  <si>
+    <t>実施された処置に関する情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>実施された処置に関する情報。</t>
+  </si>
+  <si>
+    <t>病理では省略してよい。使用する場合には、JP Core Procedureを参照する。</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=PROC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>(0008,1032)</t>
+  </si>
+  <si>
+    <t>ImagingStudy.procedureCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProcedureCodeSequence
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>実施された処置を表すコード【詳細参照】</t>
+  </si>
+  <si>
+    <t>実施された処置を表すコード。</t>
+  </si>
+  <si>
+    <t>病理では原則使用しない。</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>インスタンスにおける取得データの種類。</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part16/sect_CID_29.html</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>(0008,0061)</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.id</t>
+    <t>実行されたプロシジャー（処置等）のタイプ。</t>
+  </si>
+  <si>
+    <t>http://www.rsna.org/RadLex_Playbook.aspx</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>ImagingStudy.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+</t>
+  </si>
+  <si>
+    <t>ImagingStudyが実行された場所（画像がスキャンされた場所）を示すLocationリソースがある場合には、これを参照。</t>
+  </si>
+  <si>
+    <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
+  </si>
+  <si>
+    <t>Event.location</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role</t>
+  </si>
+  <si>
+    <t>(0008,1040) | (0040,0243)</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>EVN.7</t>
+  </si>
+  <si>
+    <t>ImagingStudy.reasonCode</t>
+  </si>
+  <si>
+    <t>DICOM画像が依頼された理由を表す1つ以上のコード【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOM画像が依頼された理由を表す1つ以上のコード。</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>研究の理由。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>(0040,1002)</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>ImagingStudy.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Pathology)
+</t>
+  </si>
+  <si>
+    <t>DICOM画像の実施理由に関する情報【詳細参照】</t>
+  </si>
+  <si>
+    <t>DICOM画像の実施理由に関する情報。</t>
+  </si>
+  <si>
+    <t>JP Core DiagnosticReportリソースを参照する。</t>
+  </si>
+  <si>
+    <t>Event.reasonReference</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>EVN.4 or by domain</t>
+  </si>
+  <si>
+    <t>ImagingStudy.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>原則、未使用</t>
+  </si>
+  <si>
+    <t>Event.note</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>ImagingStudy.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StudyDescription
+</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.extension</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.system</t>
-  </si>
-  <si>
-    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.version</t>
-  </si>
-  <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.code</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.display</t>
-  </si>
-  <si>
-    <t>システムによって定義された表現 / Representation defined by the system</t>
-  </si>
-  <si>
-    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>ImagingStudy.modality.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>ImagingStudy.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
-</t>
-  </si>
-  <si>
-    <t>DICOM画像の対象患者に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像の対象患者に関する情報。</t>
-  </si>
-  <si>
-    <t>JP Core Patientリソースを参照する。</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role</t>
-  </si>
-  <si>
-    <t>(0010/*)</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>ImagingStudy.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
-</t>
-  </si>
-  <si>
-    <t>このDICOM画像を取得するきっかけとなった情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>このDICOM画像を取得するきっかけとなった情報。</t>
-  </si>
-  <si>
-    <t>JP Core Encounterリソースを参照する。</t>
-  </si>
-  <si>
-    <t>Event.encounter</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>ImagingStudy.started</t>
-  </si>
-  <si>
-    <t>StudyDate
-StudyTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時【詳細参照】</t>
-  </si>
-  <si>
-    <t>検査開始日時、もしくは撮影装置に患者情報が届いた/入力された日時。</t>
-  </si>
-  <si>
-    <t>病理では、検体採取日時。</t>
-  </si>
-  <si>
-    <t>2011-01-01T11:01:20+03:00</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>(0008,0020)+(0008,0030)</t>
-  </si>
-  <si>
-    <t>FiveWs.init</t>
-  </si>
-  <si>
-    <t>ImagingStudy.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>他のシステムから依頼されたオーダ情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>他のシステムから依頼されたオーダ情報。</t>
-  </si>
-  <si>
-    <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
-  </si>
-  <si>
-    <t>To support grouped procedures (one imaging study supporting multiple ordered procedures, e.g. chest/abdomen/pelvis CT).</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target[classCode=DGIMG, moodCode=RQO]</t>
-  </si>
-  <si>
-    <t>(0032,1064)</t>
-  </si>
-  <si>
-    <t>FiveWs.cause</t>
-  </si>
-  <si>
-    <t>ImagingStudy.referrer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReferringPhysiciansName
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
-</t>
-  </si>
-  <si>
-    <t>依頼医師【詳細参照】</t>
-  </si>
-  <si>
-    <t>依頼医師。</t>
-  </si>
-  <si>
-    <t>病理では、原則使用しない。</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target[classCode=DGIMG, moodCode=RQO].participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>(0008,0090)+(0008,0096)</t>
-  </si>
-  <si>
-    <t>ImagingStudy.interpreter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of Physician(s) Reading Study
-</t>
-  </si>
-  <si>
-    <t>画像を診断した医師【詳細参照】</t>
-  </si>
-  <si>
-    <t>画像を診断した医師。</t>
-  </si>
-  <si>
-    <t>通常、病理医。病理では原則使用しない。</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role</t>
-  </si>
-  <si>
-    <t>(0008,1060)</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>ImagingStudy.endpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>DICOMのリソースが存在する位置【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOMのリソースが存在する位置。</t>
-  </si>
-  <si>
-    <t>DICOM WADO-RS、DICOM WADO-URI、DICOM QIDO-RSなどを指定する。</t>
-  </si>
-  <si>
-    <t>Access methods for viewing (e.g., IHE’s IID profile) or retrieving (e.g., DICOM’s WADO-URI and WADO-RS) the study or the study’s series or instances. The study-level baseLocation applies to each series in the study, unless overridden in series by a series-level baseLocation of the same type.</t>
-  </si>
-  <si>
-    <t>Not supported</t>
-  </si>
-  <si>
-    <t>ImagingStudy.numberOfSeries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NumberOfStudyRelatedSeries
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsignedInt
-</t>
-  </si>
-  <si>
-    <t>このDICOM画像検査に含まれるシリーズ数。</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=OBSSER, moodCode=EVN].repeatNumber</t>
-  </si>
-  <si>
-    <t>(0020,1206)</t>
-  </si>
-  <si>
-    <t>ImagingStudy.numberOfInstances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NumberOfStudyRelatedInstances
-</t>
-  </si>
-  <si>
-    <t>このDICOM画像に含まれるイメージ（インスタンス）の数。</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target[classCode=DGIMG, moodCode=EVN].repeatNumber</t>
-  </si>
-  <si>
-    <t>(0020,1208)</t>
-  </si>
-  <si>
-    <t>ImagingStudy.procedureReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
-</t>
-  </si>
-  <si>
-    <t>実施された処置に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>実施された処置に関する情報。</t>
-  </si>
-  <si>
-    <t>病理では省略してよい。使用する場合には、JP Core Procedureを参照する。</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=PROC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>(0008,1032)</t>
-  </si>
-  <si>
-    <t>ImagingStudy.procedureCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProcedureCodeSequence
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>実施された処置を表すコード【詳細参照】</t>
-  </si>
-  <si>
-    <t>実施された処置を表すコード。</t>
-  </si>
-  <si>
-    <t>病理では原則使用しない。</t>
-  </si>
-  <si>
-    <t>実行されたプロシジャー（処置等）のタイプ。</t>
-  </si>
-  <si>
-    <t>http://www.rsna.org/RadLex_Playbook.aspx</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>ImagingStudy.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
-</t>
-  </si>
-  <si>
-    <t>ImagingStudyが実行された場所（画像がスキャンされた場所）を示すLocationリソースがある場合には、これを参照。</t>
-  </si>
-  <si>
-    <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
-  </si>
-  <si>
-    <t>Event.location</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role</t>
-  </si>
-  <si>
-    <t>(0008,1040) | (0040,0243)</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>EVN.7</t>
-  </si>
-  <si>
-    <t>ImagingStudy.reasonCode</t>
-  </si>
-  <si>
-    <t>DICOM画像が依頼された理由を表す1つ以上のコード【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像が依頼された理由を表す1つ以上のコード。</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>研究の理由。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.reasonCode</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>(0040,1002)</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ImagingStudy.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Pathology)
-</t>
-  </si>
-  <si>
-    <t>DICOM画像の実施理由に関する情報【詳細参照】</t>
-  </si>
-  <si>
-    <t>DICOM画像の実施理由に関する情報。</t>
-  </si>
-  <si>
-    <t>JP Core DiagnosticReportリソースを参照する。</t>
-  </si>
-  <si>
-    <t>Event.reasonReference</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>EVN.4 or by domain</t>
-  </si>
-  <si>
-    <t>ImagingStudy.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>原則、未使用</t>
-  </si>
-  <si>
-    <t>Event.note</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>ImagingStudy.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StudyDescription
-</t>
-  </si>
-  <si>
     <t>DICOM画像に関する記述。</t>
   </si>
   <si>
@@ -1162,10 +1000,19 @@
     <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。</t>
   </si>
   <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>ImagingStudy.series.extension</t>
   </si>
   <si>
     <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>ImagingStudy.series.modifierExtension</t>
@@ -1249,27 +1096,6 @@
   </si>
   <si>
     <t>(0008,0060)</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.id</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.extension</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.system</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.version</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.code</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.display</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.modality.userSelected</t>
   </si>
   <si>
     <t>ImagingStudy.series.description</t>
@@ -1876,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO71"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.13671875" customWidth="true" bestFit="true"/>
@@ -1907,7 +1733,7 @@
     <col min="26" max="26" width="74.78125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="32.90234375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1918,7 +1744,7 @@
     <col min="38" max="38" width="97.94921875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="89.92578125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.41015625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3381,7 +3207,7 @@
         <v>79</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>79</v>
@@ -3396,13 +3222,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3438,13 +3262,13 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3452,10 +3276,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3463,7 +3287,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -3475,18 +3299,20 @@
         <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3535,10 +3361,10 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>89</v>
@@ -3547,19 +3373,19 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>185</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3567,21 +3393,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3590,19 +3416,19 @@
         <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3640,43 +3466,43 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AK15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3684,14 +3510,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3710,20 +3536,18 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3735,7 +3559,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3771,7 +3595,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3783,30 +3607,30 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3817,7 +3641,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -3829,18 +3653,20 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3888,46 +3714,46 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>79</v>
+        <v>216</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3946,24 +3772,24 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -4005,7 +3831,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4017,41 +3843,41 @@
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>79</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4063,18 +3889,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4122,42 +3948,42 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4168,7 +3994,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -4180,19 +4006,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4241,25 +4067,25 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4268,23 +4094,23 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4299,17 +4125,15 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4358,10 +4182,10 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>89</v>
@@ -4373,16 +4197,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4390,14 +4214,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4416,17 +4240,15 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>248</v>
       </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4475,7 +4297,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4490,16 +4312,16 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AN22" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4507,14 +4329,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4533,16 +4355,16 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4556,7 +4378,7 @@
         <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>79</v>
@@ -4592,7 +4414,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4607,16 +4429,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4624,14 +4446,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4650,20 +4472,18 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>268</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4687,13 +4507,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4711,7 +4531,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4726,16 +4546,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4743,14 +4563,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4769,18 +4589,18 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4828,7 +4648,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4843,31 +4663,31 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4886,16 +4706,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4921,13 +4741,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4945,7 +4765,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4960,16 +4780,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4977,10 +4797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5003,20 +4823,18 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>294</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5064,7 +4882,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5079,19 +4897,19 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -5103,14 +4921,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -5122,13 +4940,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5185,7 +5003,7 @@
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
@@ -5194,13 +5012,13 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>300</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
@@ -5211,14 +5029,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5237,7 +5055,7 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>304</v>
@@ -5294,7 +5112,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5340,7 +5158,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5358,11 +5176,9 @@
         <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5417,7 +5233,7 @@
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5426,13 +5242,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
@@ -5443,21 +5259,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5466,20 +5282,18 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5504,13 +5318,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5528,28 +5342,28 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="AM31" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
@@ -5560,21 +5374,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
@@ -5583,21 +5397,21 @@
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>325</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>326</v>
+        <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5645,46 +5459,46 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5697,24 +5511,26 @@
         <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>317</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5738,13 +5554,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>338</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5762,7 +5578,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5774,19 +5590,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>340</v>
+        <v>132</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5794,21 +5610,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5820,18 +5636,20 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>344</v>
+        <v>91</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5843,7 +5661,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5879,13 +5697,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -5894,38 +5712,38 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -5937,13 +5755,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>352</v>
+        <v>242</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5958,7 +5776,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5994,13 +5812,13 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
@@ -6009,13 +5827,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -6026,18 +5844,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -6052,15 +5870,17 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6070,7 +5890,7 @@
         <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>79</v>
@@ -6085,13 +5905,11 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6109,10 +5927,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -6127,10 +5945,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>359</v>
+        <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6141,21 +5959,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6167,13 +5985,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6188,7 +6006,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6224,13 +6042,13 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
@@ -6242,10 +6060,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>364</v>
+        <v>305</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6256,14 +6074,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6279,16 +6097,16 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6339,7 +6157,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>184</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6351,16 +6169,16 @@
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6371,14 +6189,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6394,21 +6212,23 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>136</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6456,7 +6276,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>193</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6468,13 +6288,13 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6488,46 +6308,44 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6551,13 +6369,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6575,28 +6393,28 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6607,18 +6425,18 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -6633,20 +6451,18 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6658,7 +6474,7 @@
         <v>79</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>79</v>
@@ -6670,13 +6486,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6694,10 +6510,10 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -6712,10 +6528,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6726,21 +6542,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6752,15 +6568,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6773,7 +6591,7 @@
         <v>79</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>79</v>
@@ -6809,13 +6627,13 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
@@ -6827,10 +6645,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6841,18 +6659,18 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6867,16 +6685,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6902,13 +6720,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6926,10 +6744,10 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -6944,10 +6762,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6958,21 +6776,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -6981,19 +6799,23 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>181</v>
+        <v>308</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7041,28 +6863,28 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>184</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7073,21 +6895,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7099,17 +6921,15 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>187</v>
+        <v>312</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7146,37 +6966,37 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7190,21 +7010,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7213,23 +7033,21 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>197</v>
+        <v>317</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7277,25 +7095,25 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>200</v>
+        <v>318</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>201</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>202</v>
+        <v>315</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7304,49 +7122,51 @@
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>205</v>
+        <v>321</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7394,25 +7214,25 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>208</v>
+        <v>323</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>201</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7421,15 +7241,15 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7452,24 +7272,26 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>261</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>214</v>
+        <v>397</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>79</v>
@@ -7487,13 +7309,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7511,7 +7333,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>216</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7523,13 +7345,13 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7538,15 +7360,15 @@
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7554,7 +7376,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7569,18 +7391,18 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>181</v>
+        <v>401</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>220</v>
+        <v>402</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7628,10 +7450,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>223</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
@@ -7640,30 +7462,30 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>224</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>225</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7674,7 +7496,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7683,23 +7505,19 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>228</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7747,25 +7565,25 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>232</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>233</v>
+        <v>409</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7774,19 +7592,19 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7802,16 +7620,16 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
+        <v>313</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7826,7 +7644,7 @@
         <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>79</v>
@@ -7862,7 +7680,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7874,16 +7692,16 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -7894,21 +7712,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>409</v>
+        <v>134</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7917,18 +7735,20 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>298</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7977,28 +7797,28 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>408</v>
+        <v>318</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -8016,7 +7836,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8029,25 +7849,25 @@
         <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>321</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
+        <v>322</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>414</v>
+        <v>138</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>415</v>
+        <v>144</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8096,7 +7916,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>412</v>
+        <v>323</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8108,13 +7928,13 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>295</v>
+        <v>132</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8128,18 +7948,18 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8151,21 +7971,23 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8177,7 +7999,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8189,13 +8011,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>421</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8213,10 +8035,10 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>89</v>
@@ -8231,10 +8053,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>422</v>
+        <v>331</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8245,18 +8067,18 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8268,19 +8090,19 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>170</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8306,14 +8128,14 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>336</v>
+        <v>265</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8330,10 +8152,10 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>89</v>
@@ -8348,7 +8170,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>429</v>
@@ -8369,14 +8191,14 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8385,10 +8207,10 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>431</v>
+        <v>242</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>432</v>
@@ -8411,7 +8233,7 @@
         <v>79</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>79</v>
@@ -8453,7 +8275,7 @@
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8502,10 +8324,10 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>438</v>
@@ -8582,1657 +8404,15 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>260</v>
+        <v>441</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO71" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:49:13+00:00</t>
+    <t>2026-08-13T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -847,13 +847,7 @@
     <t>病理では原則使用しない。</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>実行されたプロシジャー（処置等）のタイプ。</t>
-  </si>
-  <si>
-    <t>http://www.rsna.org/RadLex_Playbook.aspx</t>
+    <t>http://playbook.radlex.org/playbook/SearchRadlexAction</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1260,6 +1254,9 @@
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>パフォーマーの関与のタイプ</t>
@@ -4507,13 +4504,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4546,7 +4541,7 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>257</v>
@@ -4563,10 +4558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4589,17 +4584,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4648,7 +4643,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4663,27 +4658,27 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4709,10 +4704,10 @@
         <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>264</v>
@@ -4741,14 +4736,14 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="Y26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4765,7 +4760,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4780,16 +4775,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4797,10 +4792,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4823,16 +4818,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4882,7 +4877,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4897,27 +4892,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4940,13 +4935,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4997,7 +4992,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5012,10 +5007,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5029,14 +5024,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5055,13 +5050,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5112,7 +5107,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5130,10 +5125,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5144,10 +5139,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5170,13 +5165,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5227,7 +5222,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5245,7 +5240,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5259,10 +5254,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5285,13 +5280,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5342,7 +5337,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5360,7 +5355,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5374,10 +5369,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5406,7 +5401,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5459,7 +5454,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5477,7 +5472,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5491,14 +5486,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5520,10 +5515,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>138</v>
@@ -5578,7 +5573,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5610,14 +5605,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5639,16 +5634,16 @@
         <v>91</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5661,7 +5656,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5697,7 +5692,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>89</v>
@@ -5715,10 +5710,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5729,14 +5724,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5758,10 +5753,10 @@
         <v>242</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5776,7 +5771,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5812,7 +5807,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5830,10 +5825,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5844,14 +5839,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5873,13 +5868,13 @@
         <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5927,7 +5922,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -5948,7 +5943,7 @@
         <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -5959,14 +5954,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5985,13 +5980,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6006,7 +6001,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6042,7 +6037,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6060,10 +6055,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6074,14 +6069,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6103,10 +6098,10 @@
         <v>242</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6157,7 +6152,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6178,7 +6173,7 @@
         <v>249</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6189,10 +6184,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6218,16 +6213,16 @@
         <v>234</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6276,7 +6271,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6308,14 +6303,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6337,10 +6332,10 @@
         <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>264</v>
@@ -6369,13 +6364,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6393,7 +6388,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6411,10 +6406,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6425,10 +6420,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6454,10 +6449,10 @@
         <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>264</v>
@@ -6486,13 +6481,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6510,7 +6505,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6528,10 +6523,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6542,10 +6537,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6568,16 +6563,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6627,7 +6622,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6645,10 +6640,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6659,10 +6654,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6688,13 +6683,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6744,7 +6739,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6765,7 +6760,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6776,14 +6771,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6802,19 +6797,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>264</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6863,7 +6858,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6878,13 +6873,13 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>230</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6895,10 +6890,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6921,13 +6916,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6978,7 +6973,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6996,7 +6991,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7010,10 +7005,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7042,7 +7037,7 @@
         <v>136</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>138</v>
@@ -7095,7 +7090,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7113,7 +7108,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7127,14 +7122,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7156,10 +7151,10 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>138</v>
@@ -7214,7 +7209,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7246,10 +7241,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7275,16 +7270,16 @@
         <v>261</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>264</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7309,14 +7304,14 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>265</v>
+        <v>396</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7333,7 +7328,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7365,10 +7360,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7391,13 +7386,13 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>264</v>
@@ -7450,7 +7445,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7468,24 +7463,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7508,13 +7503,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7565,7 +7560,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7583,7 +7578,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7597,10 +7592,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7623,13 +7618,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7680,7 +7675,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7698,7 +7693,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7712,10 +7707,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7744,7 +7739,7 @@
         <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>138</v>
@@ -7797,7 +7792,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7815,7 +7810,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7829,14 +7824,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7858,10 +7853,10 @@
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>138</v>
@@ -7916,7 +7911,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7948,14 +7943,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7977,16 +7972,16 @@
         <v>91</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -7999,7 +7994,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8035,7 +8030,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>89</v>
@@ -8053,10 +8048,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8067,14 +8062,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8096,13 +8091,13 @@
         <v>170</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8128,14 +8123,14 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>265</v>
+        <v>396</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8152,7 +8147,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>89</v>
@@ -8170,10 +8165,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8184,14 +8179,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8213,13 +8208,13 @@
         <v>242</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8269,7 +8264,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8287,10 +8282,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8301,10 +8296,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8327,16 +8322,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8386,7 +8381,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8404,10 +8399,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:00:31+00:00</t>
+    <t>2026-08-13T13:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:31:56+00:00</t>
+    <t>2026-08-13T23:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="441">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:21:35+00:00</t>
+    <t>2026-08-13T23:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1346,10 +1346,7 @@
     <t>病理では、主に以下の値が指定される。VL Whole Slide Microscopy Image Storage (VL全スライド顕微鏡画像保存): 1.2.840.10008.5.1.4.1.1.77.1.6</t>
   </si>
   <si>
-    <t>インスタンスのSOPクラス。</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part04/sect_B.5.html#table_B.5-1</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1727,7 +1724,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.78125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -8125,11 +8122,9 @@
       <c r="X55" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="Y55" s="2"/>
+      <c r="Z55" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8165,10 +8160,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8179,14 +8174,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8208,13 +8203,13 @@
         <v>242</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8264,7 +8259,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8282,10 +8277,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8296,10 +8291,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8325,13 +8320,13 @@
         <v>301</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8381,7 +8376,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8399,10 +8394,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:59+00:00</t>
+    <t>2026-08-19T04:30:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
